--- a/template-paket-banyumas-cilacap.xlsx
+++ b/template-paket-banyumas-cilacap.xlsx
@@ -691,8 +691,12 @@
       <c r="Q2" s="7" t="n">
         <v>8.52</v>
       </c>
-      <c r="R2" s="8" t="n"/>
-      <c r="S2" s="8" t="n"/>
+      <c r="R2" s="8" t="n">
+        <v>-7.562931</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>109.285729</v>
+      </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -767,8 +771,12 @@
       <c r="Q3" s="7" t="n">
         <v>2.67</v>
       </c>
-      <c r="R3" s="8" t="n"/>
-      <c r="S3" s="8" t="n"/>
+      <c r="R3" s="8" t="n">
+        <v>-7.517824</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>109.294979</v>
+      </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -843,8 +851,12 @@
       <c r="Q4" s="7" t="n">
         <v>5.89</v>
       </c>
-      <c r="R4" s="8" t="n"/>
-      <c r="S4" s="8" t="n"/>
+      <c r="R4" s="8" t="n">
+        <v>-7.463727</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>109.219238</v>
+      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -919,8 +931,12 @@
       <c r="Q5" s="7" t="n">
         <v>13.59</v>
       </c>
-      <c r="R5" s="8" t="n"/>
-      <c r="S5" s="8" t="n"/>
+      <c r="R5" s="8" t="n">
+        <v>-7.407424</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>109.137325</v>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli; lewat jadwal kontrak - contoh status Terlambat</t>
@@ -995,8 +1011,12 @@
       <c r="Q6" s="7" t="n">
         <v>9.09</v>
       </c>
-      <c r="R6" s="8" t="n"/>
-      <c r="S6" s="8" t="n"/>
+      <c r="R6" s="8" t="n">
+        <v>-7.512563</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>109.203632</v>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli; belum mulai (SPMK belum terbit)</t>
@@ -1071,8 +1091,12 @@
       <c r="Q7" s="7" t="n">
         <v>5.82</v>
       </c>
-      <c r="R7" s="8" t="n"/>
-      <c r="S7" s="8" t="n"/>
+      <c r="R7" s="8" t="n">
+        <v>-7.483007</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>109.299163</v>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1147,8 +1171,12 @@
       <c r="Q8" s="7" t="n">
         <v>4.89</v>
       </c>
-      <c r="R8" s="8" t="n"/>
-      <c r="S8" s="8" t="n"/>
+      <c r="R8" s="8" t="n">
+        <v>-7.449242</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>109.28</v>
+      </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1223,8 +1251,12 @@
       <c r="Q9" s="7" t="n">
         <v>8.27</v>
       </c>
-      <c r="R9" s="8" t="n"/>
-      <c r="S9" s="8" t="n"/>
+      <c r="R9" s="8" t="n">
+        <v>-7.520214</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>109.33011</v>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1299,8 +1331,12 @@
       <c r="Q10" s="7" t="n">
         <v>12.11</v>
       </c>
-      <c r="R10" s="8" t="n"/>
-      <c r="S10" s="8" t="n"/>
+      <c r="R10" s="8" t="n">
+        <v>-7.697601</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>109.055579</v>
+      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1375,8 +1411,12 @@
       <c r="Q11" s="7" t="n">
         <v>7.59</v>
       </c>
-      <c r="R11" s="8" t="n"/>
-      <c r="S11" s="8" t="n"/>
+      <c r="R11" s="8" t="n">
+        <v>-7.638798</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>109.034413</v>
+      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1451,8 +1491,12 @@
       <c r="Q12" s="7" t="n">
         <v>4.37</v>
       </c>
-      <c r="R12" s="8" t="n"/>
-      <c r="S12" s="8" t="n"/>
+      <c r="R12" s="8" t="n">
+        <v>-7.65994</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>109.103651</v>
+      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli; contoh deviasi kritis</t>
@@ -1527,8 +1571,12 @@
       <c r="Q13" s="7" t="n">
         <v>4.43</v>
       </c>
-      <c r="R13" s="8" t="n"/>
-      <c r="S13" s="8" t="n"/>
+      <c r="R13" s="8" t="n">
+        <v>-7.691322</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>109.039477</v>
+      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli; dua ruas dalam satu paket (pisahkan dengan titik koma)</t>
@@ -1679,8 +1727,12 @@
       <c r="Q15" s="7" t="n">
         <v>3.4</v>
       </c>
-      <c r="R15" s="8" t="n"/>
-      <c r="S15" s="8" t="n"/>
+      <c r="R15" s="8" t="n">
+        <v>-7.676503</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>109.027453</v>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1755,8 +1807,12 @@
       <c r="Q16" s="7" t="n">
         <v>2.9</v>
       </c>
-      <c r="R16" s="8" t="n"/>
-      <c r="S16" s="8" t="n"/>
+      <c r="R16" s="8" t="n">
+        <v>-7.640003</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>109.114721</v>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli</t>
@@ -1835,8 +1891,12 @@
       <c r="Q17" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="R17" s="8" t="n"/>
-      <c r="S17" s="8" t="n"/>
+      <c r="R17" s="8" t="n">
+        <v>-7.735517</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>108.997535</v>
+      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
           <t>CONTOH (data fiktif) - ganti/hapus sebelum unggah data asli; contoh kontrak diputus (status manual)</t>
@@ -1870,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1926,94 +1986,106 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Ruas</t>
+          <t>Koordinat</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Isi 'ID Ruas' (sama dengan id di data-ruas.js, mis. 33-banyumas-buntu) atau nama ruas persis agar paket tampil sebagai garis berwarna di peta. Beberapa ruas: pisahkan dengan titik koma (;). Paket tanpa ruas (mis. jembatan) cukup isi Latitude &amp; Longitude.</t>
+          <t>Latitude/Longitude (desimal, mis. -7.525000 / 109.290000) = titik tengah paket. Opsional bila ID Ruas terisi (garis diambil dari data ruas); wajib bila paket tidak punya ruas (mis. jembatan). Pada data contoh diisi titik tengah ruas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Tanggal</t>
+          <t>Ruas</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Gunakan format tanggal Excel, atau teks dd/mm/yyyy, yyyy-mm-dd, atau '5 Maret 2026'.</t>
+          <t>Isi 'ID Ruas' (sama dengan id di data-ruas.js, mis. 33-banyumas-buntu) atau nama ruas persis agar paket tampil sebagai garis berwarna di peta. Beberapa ruas: pisahkan dengan titik koma (;). Paket tanpa ruas (mis. jembatan) cukup isi Latitude &amp; Longitude.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Progres</t>
+          <t>Tanggal</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Angka 0-100 (tanpa tanda %). Progres Fisik &gt;= 100 otomatis berstatus Selesai.</t>
+          <t>Gunakan format tanggal Excel, atau teks dd/mm/yyyy, yyyy-mm-dd, atau '5 Maret 2026'.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Status (opsional)</t>
+          <t>Progres</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Kosongkan - status dihitung otomatis: Belum Mulai, Berjalan, Terlambat (lewat tanggal selesai, fisik &lt;100), Selesai. Isi hanya 'Putus Kontrak' atau 'Selesai' bila ingin menimpa.</t>
+          <t>Angka 0-100 (tanpa tanda %). Progres Fisik &gt;= 100 otomatis berstatus Selesai.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Deviasi</t>
+          <t>Status (opsional)</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Deviasi = Progres Fisik - Rencana (linear terhadap waktu kontrak). &gt;= 0 Sesuai; 0 s.d. -10 Waspada; lebih buruk dari -10 Kritis.</t>
+          <t>Kosongkan - status dihitung otomatis: Belum Mulai, Berjalan, Terlambat (lewat tanggal selesai, fisik &lt;100), Selesai. Isi hanya 'Putus Kontrak' atau 'Selesai' bila ingin menimpa.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Nilai</t>
+          <t>Deviasi</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nilai Kontrak dalam rupiah penuh (angka). Teks 'Rp 1.250.000.000' juga terbaca.</t>
+          <t>Deviasi = Progres Fisik - Rencana (linear terhadap waktu kontrak). &gt;= 0 Sesuai; 0 s.d. -10 Waspada; lebih buruk dari -10 Kritis.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Catatan data contoh</t>
+          <t>Nilai</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Semua nilai, penyedia, dan nomor kontrak pada baris contoh adalah FIKTIF, hanya untuk memperlihatkan format. Nama &amp; ID ruas diambil dari data PETAQU (Banyumas &amp; Cilacap).</t>
+          <t>Nilai Kontrak dalam rupiah penuh (angka). Teks 'Rp 1.250.000.000' juga terbaca.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>Catatan data contoh</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Semua nilai, penyedia, dan nomor kontrak pada baris contoh adalah FIKTIF, hanya untuk memperlihatkan format. Nama &amp; ID ruas diambil dari data PETAQU (Banyumas &amp; Cilacap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>Warna sel</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Teks biru = isian yang diedit pengguna (konvensi input).</t>
         </is>
